--- a/buckman/validation/2024/expected_outputs/Table_5_expected.xlsx
+++ b/buckman/validation/2024/expected_outputs/Table_5_expected.xlsx
@@ -1,37 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bradwolaver\projects\rg\santafe\buckman\validation\2024\expected_outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2279E4-DE81-4EF2-BED4-17D280DC094B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="10875" yWindow="3510" windowWidth="14235" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Cienega Springs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="La Cienega Springs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total (AF)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +63,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,192 +388,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total (AF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>2004</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>0.45</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2005</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>0.66</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>2006</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>0.83</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>2007</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>0.99</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>2008</v>
       </c>
-      <c r="B6" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B6">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>2009</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1.32</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>2010</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1.49</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>2011</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1.65</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>2012</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1.82</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>2013</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1.97</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>2014</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>2.13</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>2015</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>2.29</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>2016</v>
       </c>
-      <c r="B14" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="B14">
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>2017</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>2.6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>2018</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>2.75</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>2019</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>2.9</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>2020</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>3.06</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>2021</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>3.21</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>2022</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>3.37</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>2023</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>3.54</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>2024</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>3.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2025</v>
+      </c>
+      <c r="B23">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2028</v>
+      </c>
+      <c r="B26" s="2">
+        <v>4.4459999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2029</v>
+      </c>
+      <c r="B27" s="2">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2030</v>
+      </c>
+      <c r="B28" s="2">
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/buckman/validation/2024/expected_outputs/Table_5_expected.xlsx
+++ b/buckman/validation/2024/expected_outputs/Table_5_expected.xlsx
@@ -1,60 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bradwolaver\projects\rg\santafe\buckman\validation\2024\expected_outputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2279E4-DE81-4EF2-BED4-17D280DC094B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="10875" yWindow="3510" windowWidth="14235" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="La Cienega Springs" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 5 - La Cienega Springs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total (AF)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -63,44 +67,106 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <bottom style="hair"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -388,232 +454,586 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Annual Δ (AF)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cumul check</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Δ (B−D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>2004</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4" t="n">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="C2" s="5">
+        <f>B2</f>
+        <v/>
+      </c>
+      <c r="D2" s="5">
+        <f>C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="5">
+        <f>B2-D2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>2005</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4" t="n">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="C3" s="5">
+        <f>B3-B2</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>D2+C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>B3-D3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>2006</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4" t="n">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="C4" s="5">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>D3+C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>B4-D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>2007</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4" t="n">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="C5" s="5">
+        <f>B5-B4</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>D4+C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>B5-D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>2008</v>
       </c>
-      <c r="B6">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B6" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C6" s="5">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>D5+C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>B6-D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>2009</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4" t="n">
         <v>1.32</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="C7" s="5">
+        <f>B7-B6</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>D6+C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>B7-D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4" t="n">
         <v>1.49</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="C8" s="5">
+        <f>B8-B7</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>D7+C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>B8-D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>2011</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4" t="n">
         <v>1.65</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="C9" s="5">
+        <f>B9-B8</f>
+        <v/>
+      </c>
+      <c r="D9" s="5">
+        <f>D8+C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="5">
+        <f>B9-D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>2012</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4" t="n">
         <v>1.82</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="C10" s="5">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>D9+C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>B10-D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>2013</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4" t="n">
         <v>1.97</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="C11" s="5">
+        <f>B11-B10</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>D10+C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>B11-D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>2014</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4" t="n">
         <v>2.13</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="C12" s="5">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>D11+C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>B12-D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>2015</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4" t="n">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="C13" s="5">
+        <f>B13-B12</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>D12+C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>B13-D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>2016</v>
       </c>
-      <c r="B14">
-        <v>2.4500000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B14" s="4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C14" s="5">
+        <f>B14-B13</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>D13+C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>B14-D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>2017</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4" t="n">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="C15" s="5">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>D14+C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>B15-D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>2018</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4" t="n">
         <v>2.75</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="C16" s="5">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>D15+C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>B16-D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>2019</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4" t="n">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="C17" s="5">
+        <f>B17-B16</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>D16+C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>B17-D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4" t="n">
         <v>3.06</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="C18" s="5">
+        <f>B18-B17</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>D17+C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>B18-D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4" t="n">
         <v>3.21</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="C19" s="5">
+        <f>B19-B18</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>D18+C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>B19-D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4" t="n">
         <v>3.37</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="C20" s="5">
+        <f>B20-B19</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>D19+C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>B20-D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4" t="n">
         <v>3.54</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="C21" s="5">
+        <f>B21-B20</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>D20+C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>B21-D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="B22">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="B22" s="4" t="n">
+        <v>3.741411570247934</v>
+      </c>
+      <c r="C22" s="5">
+        <f>B22-B21</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>D21+C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>B22-D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="B23">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="B23" s="4" t="n">
+        <v>3.91846214876033</v>
+      </c>
+      <c r="C23" s="5">
+        <f>B23-B22</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>D22+C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>B23-D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B24" s="2">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="B24" s="4" t="n">
+        <v>4.096159338842975</v>
+      </c>
+      <c r="C24" s="5">
+        <f>B24-B23</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>D23+C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>B24-D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>2027</v>
       </c>
-      <c r="B25" s="2">
-        <v>4.2699999999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="B25" s="4" t="n">
+        <v>4.26811041322314</v>
+      </c>
+      <c r="C25" s="5">
+        <f>B25-B24</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>D24+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>B25-D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>2028</v>
       </c>
-      <c r="B26" s="2">
-        <v>4.4459999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="B26" s="4" t="n">
+        <v>4.455302479338843</v>
+      </c>
+      <c r="C26" s="5">
+        <f>B26-B25</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>D25+C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>B26-D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>2029</v>
       </c>
-      <c r="B27" s="2">
-        <v>4.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="B27" s="4" t="n">
+        <v>4.619115371900826</v>
+      </c>
+      <c r="C27" s="5">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>D26+C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="5">
+        <f>B27-D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
         <v>2030</v>
       </c>
-      <c r="B28" s="2">
-        <v>4.8</v>
+      <c r="B28" s="4" t="n">
+        <v>4.795160330578512</v>
+      </c>
+      <c r="C28" s="5">
+        <f>B28-B27</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>D27+C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>B28-D28</f>
+        <v/>
       </c>
     </row>
   </sheetData>
